--- a/backend/test_codes/table_analyzer_codes/outputs2/b5_040_final.xlsx
+++ b/backend/test_codes/table_analyzer_codes/outputs2/b5_040_final.xlsx
@@ -425,14 +425,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
@@ -524,12 +524,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>-人民币百万元百分比除外</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>d</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>ea</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;资本</t>
+          <t>可用的稳定资金</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3927743</t>
+          <t>e</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3927743</t>
+          <t>资本</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3889504</t>
+          <t>3927743</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3889504</t>
+          <t>3927743</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本</t>
+          <t>可用的稳定资金&gt;&gt;资本</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.927.743</t>
+          <t>3889504</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本</t>
+          <t>可用的稳定资金&gt;&gt;资本</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.927.743</t>
+          <t>3889504</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3.889.504</t>
+          <t>监管资本</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3889504</t>
+          <t>3.927.743</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
+          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7190311</t>
+          <t>3.927.743</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
+          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>9612211</t>
+          <t>3.889.504</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
+          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;监管资本</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>331138</t>
+          <t>3889504</t>
         </is>
       </c>
     </row>
@@ -1619,17 +1619,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
+          <t>可用的稳定资金&gt;&gt;资本&gt;&gt;其他资本工具</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>794435</t>
+          <t>其他资本工具</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>16379.2816995821</t>
+          <t>来自零售和小企业客户的存款</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>9401770</t>
+          <t>7190311</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>411958</t>
+          <t>9612211</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>848019</t>
+          <t>331138</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>16136127</t>
+          <t>794435</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3264551</t>
+          <t>16379.2816995821</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18.430</t>
+          <t>9401770</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8.069</t>
+          <t>411958</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6.568</t>
+          <t>848019</t>
         </is>
       </c>
     </row>
@@ -2169,12 +2169,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>31330653165392</t>
+          <t>16136127</t>
         </is>
       </c>
     </row>
@@ -2224,17 +2224,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17.357</t>
+          <t>稳定存款</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>7.508</t>
+          <t>3264551</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6.950</t>
+          <t>18.430</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>3037695</t>
+          <t>8.069</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.925.760</t>
+          <t>6.568</t>
         </is>
       </c>
     </row>
@@ -2499,12 +2499,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9.593.781</t>
+          <t>31330653165392</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>323.069</t>
+          <t>17.357</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>787.867</t>
+          <t>7.508</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>13.246.2163830429</t>
+          <t>6.950</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;稳定存款</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>9384.413</t>
+          <t>3037695</t>
         </is>
       </c>
     </row>
@@ -2774,17 +2774,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>404.450</t>
+          <t>欠稳定存款</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>841.069</t>
+          <t>3.925.760</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;来自零售和小企业客户的存款&gt;&gt;欠稳定存款</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>13.098.432</t>
+          <t>9.593.781</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1750282</t>
+          <t>323.069</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13221187</t>
+          <t>787.867</t>
         </is>
       </c>
     </row>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1755405</t>
+          <t>13.246.2163830429</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>851151</t>
+          <t>9384.413</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>7.523.9642616549</t>
+          <t>404.450</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>13066185</t>
+          <t>841.069</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资</t>
+          <t>可用的稳定资金&gt;&gt;欠稳定存款</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1871641</t>
+          <t>13.098.432</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>922785</t>
+          <t>批发融资</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8153873</t>
+          <t>1750282</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1592324</t>
+          <t>13221187</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>5196931</t>
+          <t>1755405</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>48.978</t>
+          <t>851151</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.523.9642616549</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>34191232453200</t>
+          <t>13066185</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>5152424</t>
+          <t>1871641</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>75.039</t>
+          <t>922785</t>
         </is>
       </c>
     </row>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;批发融资</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8153873</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>3840335</t>
+          <t>业务关系存款</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>157958</t>
+          <t>1592324</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8024256</t>
+          <t>5196931</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1706427</t>
+          <t>48.978</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>851145</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>4104841163349</t>
+          <t>34191232453200</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>7913761</t>
+          <t>5152424</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1796602</t>
+          <t>75.039</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>922781</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;业务关系存款</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4313538</t>
+          <t>3840335</t>
         </is>
       </c>
     </row>
@@ -4424,17 +4424,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>281494</t>
+          <t>其他批发融资</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>212635</t>
+          <t>157958</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>324842</t>
+          <t>8024256</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>327334</t>
+          <t>1706427</t>
         </is>
       </c>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>248565</t>
+          <t>851145</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4699,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>222057</t>
+          <t>4104841163349</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>120375</t>
+          <t>7913761</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;其他负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>171134</t>
+          <t>1796602</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>103825</t>
+          <t>922781</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债</t>
+          <t>可用的稳定资金&gt;&gt;批发融资&gt;&gt;其他批发融资</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>60.269</t>
+          <t>4313538</t>
         </is>
       </c>
     </row>
@@ -4974,17 +4974,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;相互依存的负债</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>281494</t>
+          <t>相互依存的负债</t>
         </is>
       </c>
     </row>
@@ -5029,17 +5029,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>212635</t>
+          <t>其他负债</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>221017</t>
+          <t>281494</t>
         </is>
       </c>
     </row>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>327334</t>
+          <t>212635</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>248565</t>
+          <t>324842</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>222057</t>
+          <t>327334</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>60.106</t>
+          <t>248565</t>
         </is>
       </c>
     </row>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>171134</t>
+          <t>222057</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>28158322</t>
+          <t>120375</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计</t>
+          <t>可用的稳定资金&gt;&gt;其他负债</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>28350638</t>
+          <t>171134</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>所需的稳定资金</t>
+          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2512583</t>
+          <t>净稳定资金比例衍生产品负债</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>所需的稳定资金</t>
+          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2554976</t>
+          <t>103825</t>
         </is>
       </c>
     </row>
@@ -5634,12 +5634,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;净稳定资金比例衍生产品负债</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>51698</t>
+          <t>60.269</t>
         </is>
       </c>
     </row>
@@ -5689,17 +5689,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>以上未包括的所有其它负债和权益</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>7.484</t>
+          <t>281494</t>
         </is>
       </c>
     </row>
@@ -5799,12 +5799,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>212635</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4144864428</t>
+          <t>221017</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>327334</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>248565</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>222057</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算后数值</t>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>53624</t>
+          <t>60.106</t>
         </is>
       </c>
     </row>
@@ -6129,12 +6129,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;以上未包括的所有其它负债和权益</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1132786</t>
+          <t>171134</t>
         </is>
       </c>
     </row>
@@ -6184,17 +6184,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>6941603</t>
+          <t>可用的稳定资金合计</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>3570517</t>
+          <t>28158322</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>可用的稳定资金&gt;&gt;可用的稳定资金合计</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>16039685</t>
+          <t>28350638</t>
         </is>
       </c>
     </row>
@@ -6349,17 +6349,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>所需的稳定资金</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>176834651091884</t>
+          <t>净稳定资金比例合格优质流动性资产</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>所需的稳定资金</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>7224215</t>
+          <t>2512583</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>所需的稳定资金</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>3380129</t>
+          <t>2554976</t>
         </is>
       </c>
     </row>
@@ -6514,17 +6514,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>16096481</t>
+          <t>存放在金融机构的业务关系存款</t>
         </is>
       </c>
     </row>
@@ -6569,35 +6569,1025 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>51698</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>17931</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>7.484</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>4144864428</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>33752</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;净稳定资金比例合格优质流动资产</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>53624</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>贷款和证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;无期限</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>1132786</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>6941603</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>3570517</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>16039685</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>176834651091884</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6个月</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>7224215</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;6-12个月</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>3380129</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2024年第三季度&gt;&gt;折算前数值&gt;&gt;≥1年</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>16096481</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>净稳定资金比例</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>所需的稳定资金&gt;&gt;存放在金融机构的业务关系存款</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>2024年第三季度&gt;&gt;折算后数值</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>发生额</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>百万元</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>2024年</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>17678317</t>
         </is>
